--- a/data/reels_stories.xlsx
+++ b/data/reels_stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Data/Work/Education/learning-hub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FA53C5-DE7C-CE49-8102-03E3E44FD1C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9EC674-7FF7-E344-BC3E-42BA81582D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
   <si>
     <t>id</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>assets/video/CNY01.mp4</t>
+  </si>
+  <si>
+    <t>assets/video/midautumn01.mp4</t>
   </si>
 </sst>
 </file>
@@ -847,7 +850,7 @@
         <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
@@ -1102,7 +1105,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L1 A3:L11 A2:D2 F2:L2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L1 A3:L4 A2:D2 F2:L2 A6:L11 A5:D5 F5:L5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/reels_stories.xlsx
+++ b/data/reels_stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Data/Work/Education/learning-hub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9EC674-7FF7-E344-BC3E-42BA81582D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE6A679-CB10-D545-8AF3-6601216D931E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -305,6 +305,27 @@
   </si>
   <si>
     <t>assets/video/midautumn01.mp4</t>
+  </si>
+  <si>
+    <t>qixi</t>
+  </si>
+  <si>
+    <t>看牛郎织女星 - Stargazing Love</t>
+  </si>
+  <si>
+    <t>assets/video/Qixi01.mp4</t>
+  </si>
+  <si>
+    <t>仰望星空，寻找牛郎织女</t>
+  </si>
+  <si>
+    <t>yǎng wàng xīng kōng, xún zhǎo niú láng zhī nǚ</t>
+  </si>
+  <si>
+    <t>Look up at the starry night sky for the lovers!</t>
+  </si>
+  <si>
+    <t>မိုးကောင်းကင်ထက်မှ ချစ်သူကြယ်ပွင့်နှစ်ပွင့်!</t>
   </si>
 </sst>
 </file>
@@ -681,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -1100,6 +1121,44 @@
       </c>
       <c r="L11" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/reels_stories.xlsx
+++ b/data/reels_stories.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Data/Work/Education/learning-hub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE6A679-CB10-D545-8AF3-6601216D931E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335A259F-40C4-6341-8A12-6DAF666AE880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="103">
   <si>
     <t>id</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>မိုးကောင်းကင်ထက်မှ ချစ်သူကြယ်ပွင့်နှစ်ပွင့်!</t>
+  </si>
+  <si>
+    <t>assets/video/culture01.mp4</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1026,7 @@
         <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>102</v>
       </c>
       <c r="F9" t="s">
         <v>75</v>
@@ -1164,7 +1167,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:L1 A3:L4 A2:D2 F2:L2 A6:L11 A5:D5 F5:L5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:L1 A3:L4 A2:D2 F2:L2 A6:L8 A5:D5 F5:L5 A10:L11 A9:D9 F9:L9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>